--- a/data/hex_xlsx/RELAIS.HE.xlsx
+++ b/data/hex_xlsx/RELAIS.HE.xlsx
@@ -1125,7 +1125,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1206,6 +1206,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -6634,9 +6637,15 @@
       <c r="F86" s="19">
         <v>60.49</v>
       </c>
-      <c r="G86" s="18"/>
-      <c r="H86" s="18"/>
-      <c r="I86" s="18"/>
+      <c r="G86" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="H86" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="I86" s="27">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
@@ -10827,904 +10836,904 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="31">
         <v>4482.81</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>4408.93</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>3472.16</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>6126.0</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>2890.57</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="31">
         <v>1656.31</v>
       </c>
-      <c r="H21" s="31"/>
+      <c r="H21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="30" t="s">
         <v>278</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="31">
         <v>4692.99</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <v>3985.21</v>
       </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="31">
         <v>2837.71</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <v>2737.94</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <v>1939.06</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <v>4724.01</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <v>2590.29</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <v>1316.32</v>
       </c>
-      <c r="H24" s="31"/>
+      <c r="H24" s="32"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="31">
         <v>3271.24</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>2869.22</v>
       </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="31">
         <v>156.5</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>151.0</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>106.94</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>263.3</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>154.0</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="33">
         <v>81.18</v>
       </c>
-      <c r="H27" s="31"/>
+      <c r="H27" s="32"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="31">
         <v>183.56</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <v>163.19</v>
       </c>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="34">
         <v>12.57</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>10.81</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>14.7</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>1.89</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="34">
         <v>6.43</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>1.05</v>
       </c>
-      <c r="H30" s="33"/>
+      <c r="H30" s="34"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="34">
         <v>7.79</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <v>6.15</v>
       </c>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="28" t="s">
         <v>287</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="34">
         <v>3.31</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="34">
         <v>2.96</v>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="34">
         <v>3.53</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="34">
         <v>1.14</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="34">
         <v>0.68</v>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="34">
         <v>0.0</v>
       </c>
-      <c r="H33" s="33"/>
+      <c r="H33" s="34"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="34">
         <v>2.05</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="34">
         <v>1.59</v>
       </c>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="B35" s="33">
+      <c r="B35" s="34">
         <v>3.31</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="34">
         <v>2.96</v>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="34">
         <v>3.53</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="34">
         <v>1.14</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="34">
         <v>0.68</v>
       </c>
-      <c r="G35" s="33">
+      <c r="G35" s="34">
         <v>0.0</v>
       </c>
-      <c r="H35" s="33"/>
+      <c r="H35" s="34"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="B36" s="33">
+      <c r="B36" s="34">
         <v>2.05</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="34">
         <v>1.59</v>
       </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="30" t="s">
         <v>293</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="33">
         <v>2.05</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <v>2.21</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="33">
         <v>1.78</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="33">
         <v>4.53</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="33">
         <v>3.44</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="33">
         <v>2.1</v>
       </c>
-      <c r="H38" s="31"/>
+      <c r="H38" s="32"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="30" t="s">
         <v>294</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="33">
         <v>2.75</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="33">
         <v>2.82</v>
       </c>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="32">
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="33">
         <v>18.65</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="33">
         <v>14.22</v>
       </c>
-      <c r="H41" s="31"/>
+      <c r="H41" s="32"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="27" t="s">
+      <c r="A42" s="28" t="s">
         <v>297</v>
       </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="30" t="s">
         <v>298</v>
       </c>
-      <c r="B43" s="32">
+      <c r="B43" s="33">
         <v>0.75</v>
       </c>
-      <c r="C43" s="32">
+      <c r="C43" s="33">
         <v>0.86</v>
       </c>
-      <c r="D43" s="32">
+      <c r="D43" s="33">
         <v>0.71</v>
       </c>
-      <c r="E43" s="32">
+      <c r="E43" s="33">
         <v>2.03</v>
       </c>
-      <c r="F43" s="32">
+      <c r="F43" s="33">
         <v>1.92</v>
       </c>
-      <c r="G43" s="32">
+      <c r="G43" s="33">
         <v>1.35</v>
       </c>
-      <c r="H43" s="31"/>
+      <c r="H43" s="32"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
+      <c r="A44" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="33">
         <v>1.14</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <v>1.28</v>
       </c>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="31"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="30" t="s">
         <v>301</v>
       </c>
-      <c r="B46" s="32">
+      <c r="B46" s="33">
         <v>7.95</v>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="33">
         <v>9.25</v>
       </c>
-      <c r="D46" s="32">
+      <c r="D46" s="33">
         <v>6.8</v>
       </c>
-      <c r="E46" s="32">
+      <c r="E46" s="33">
         <v>52.8</v>
       </c>
-      <c r="F46" s="32">
+      <c r="F46" s="33">
         <v>15.55</v>
       </c>
-      <c r="G46" s="32">
+      <c r="G46" s="33">
         <v>95.09</v>
       </c>
-      <c r="H46" s="31"/>
+      <c r="H46" s="32"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="30" t="s">
         <v>302</v>
       </c>
-      <c r="B47" s="32">
+      <c r="B47" s="33">
         <v>12.84</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="33">
         <v>16.25</v>
       </c>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="B49" s="32">
+      <c r="B49" s="33">
         <v>6.43</v>
       </c>
-      <c r="C49" s="32">
+      <c r="C49" s="33">
         <v>7.62</v>
       </c>
-      <c r="D49" s="32">
+      <c r="D49" s="33">
         <v>6.83</v>
       </c>
-      <c r="E49" s="32">
+      <c r="E49" s="33">
         <v>21.58</v>
       </c>
-      <c r="F49" s="32">
+      <c r="F49" s="33">
         <v>16.43</v>
       </c>
-      <c r="G49" s="32">
+      <c r="G49" s="33">
         <v>22.15</v>
       </c>
-      <c r="H49" s="31"/>
+      <c r="H49" s="32"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="29" t="s">
+      <c r="A50" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="33">
         <v>10.48</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <v>12.68</v>
       </c>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="27" t="s">
+      <c r="A51" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="B52" s="32">
+      <c r="B52" s="33">
         <v>12.99</v>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="33">
         <v>17.82</v>
       </c>
-      <c r="D52" s="32">
+      <c r="D52" s="33">
         <v>18.36</v>
       </c>
-      <c r="E52" s="32">
+      <c r="E52" s="33">
         <v>62.62</v>
       </c>
-      <c r="F52" s="32">
+      <c r="F52" s="33">
         <v>35.64</v>
       </c>
-      <c r="G52" s="30">
+      <c r="G52" s="31">
         <v>348.4</v>
       </c>
-      <c r="H52" s="31"/>
+      <c r="H52" s="32"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
+      <c r="A53" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="33">
         <v>24.61</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="33">
         <v>33.63</v>
       </c>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="27" t="s">
+      <c r="A54" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="28"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="B55" s="32">
+      <c r="B55" s="33">
         <v>13.44</v>
       </c>
-      <c r="C55" s="32">
+      <c r="C55" s="33">
         <v>17.81</v>
       </c>
-      <c r="D55" s="32">
+      <c r="D55" s="33">
         <v>18.85</v>
       </c>
-      <c r="E55" s="32">
+      <c r="E55" s="33">
         <v>61.19</v>
       </c>
-      <c r="F55" s="32">
+      <c r="F55" s="33">
         <v>35.64</v>
       </c>
-      <c r="G55" s="30">
+      <c r="G55" s="31">
         <v>348.4</v>
       </c>
-      <c r="H55" s="31"/>
+      <c r="H55" s="32"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="33">
         <v>2.75</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="33">
         <v>2.82</v>
       </c>
-      <c r="D56" s="31"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="31"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="30" t="s">
         <v>313</v>
       </c>
-      <c r="B58" s="32">
+      <c r="B58" s="33">
         <v>0.37</v>
       </c>
-      <c r="C58" s="32">
+      <c r="C58" s="33">
         <v>0.49</v>
       </c>
-      <c r="D58" s="32">
+      <c r="D58" s="33">
         <v>0.57</v>
       </c>
-      <c r="E58" s="32">
+      <c r="E58" s="33">
         <v>34.16</v>
       </c>
-      <c r="F58" s="32">
+      <c r="F58" s="33">
         <v>0.02</v>
       </c>
-      <c r="G58" s="34">
+      <c r="G58" s="35">
         <v>-3.89</v>
       </c>
-      <c r="H58" s="31"/>
+      <c r="H58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="29" t="s">
+      <c r="A59" s="30" t="s">
         <v>314</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="33">
         <v>0.22</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="33">
         <v>1.24</v>
       </c>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="27" t="s">
+      <c r="A60" s="28" t="s">
         <v>315</v>
       </c>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="30" t="s">
         <v>316</v>
       </c>
-      <c r="B61" s="32">
+      <c r="B61" s="33">
         <v>1.18</v>
       </c>
-      <c r="C61" s="32">
+      <c r="C61" s="33">
         <v>1.39</v>
       </c>
-      <c r="D61" s="32">
+      <c r="D61" s="33">
         <v>1.27</v>
       </c>
-      <c r="E61" s="32">
+      <c r="E61" s="33">
         <v>2.57</v>
       </c>
-      <c r="F61" s="32">
+      <c r="F61" s="33">
         <v>2.14</v>
       </c>
-      <c r="G61" s="32">
+      <c r="G61" s="33">
         <v>1.7</v>
       </c>
-      <c r="H61" s="31"/>
+      <c r="H61" s="32"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="29" t="s">
+      <c r="A62" s="30" t="s">
         <v>317</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="33">
         <v>1.62</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <v>1.76</v>
       </c>
-      <c r="D62" s="31"/>
-      <c r="E62" s="31"/>
-      <c r="F62" s="31"/>
-      <c r="G62" s="31"/>
-      <c r="H62" s="31"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="27" t="s">
+      <c r="A63" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="B63" s="28"/>
-      <c r="C63" s="28"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="28"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="29"/>
+      <c r="E63" s="29"/>
+      <c r="F63" s="29"/>
+      <c r="G63" s="29"/>
+      <c r="H63" s="29"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="B64" s="32">
+      <c r="B64" s="33">
         <v>7.51</v>
       </c>
-      <c r="C64" s="32">
+      <c r="C64" s="33">
         <v>9.37</v>
       </c>
-      <c r="D64" s="32">
+      <c r="D64" s="33">
         <v>9.43</v>
       </c>
-      <c r="E64" s="32">
+      <c r="E64" s="33">
         <v>20.76</v>
       </c>
-      <c r="F64" s="32">
+      <c r="F64" s="33">
         <v>14.72</v>
       </c>
-      <c r="G64" s="32">
+      <c r="G64" s="33">
         <v>13.03</v>
       </c>
-      <c r="H64" s="31"/>
+      <c r="H64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="29" t="s">
+      <c r="A65" s="30" t="s">
         <v>320</v>
       </c>
-      <c r="B65" s="32">
+      <c r="B65" s="33">
         <v>11.32</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="33">
         <v>12.88</v>
       </c>
-      <c r="D65" s="31"/>
-      <c r="E65" s="31"/>
-      <c r="F65" s="31"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="31"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="27" t="s">
+      <c r="A66" s="28" t="s">
         <v>321</v>
       </c>
-      <c r="B66" s="28"/>
-      <c r="C66" s="28"/>
-      <c r="D66" s="28"/>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="28"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="29"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="29"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="29" t="s">
+      <c r="A67" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="B67" s="32">
+      <c r="B67" s="33">
         <v>10.94</v>
       </c>
-      <c r="C67" s="32">
+      <c r="C67" s="33">
         <v>12.88</v>
       </c>
-      <c r="D67" s="32">
+      <c r="D67" s="33">
         <v>11.51</v>
       </c>
-      <c r="E67" s="32">
+      <c r="E67" s="33">
         <v>52.65</v>
       </c>
-      <c r="F67" s="32">
+      <c r="F67" s="33">
         <v>17.14</v>
       </c>
-      <c r="G67" s="32">
+      <c r="G67" s="33">
         <v>93.59</v>
       </c>
-      <c r="H67" s="31"/>
+      <c r="H67" s="32"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="B68" s="32">
+      <c r="B68" s="33">
         <v>16.35</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="33">
         <v>20.04</v>
       </c>
-      <c r="D68" s="31"/>
-      <c r="E68" s="31"/>
-      <c r="F68" s="31"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="31"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="27" t="s">
+      <c r="A69" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="29" t="s">
+      <c r="A70" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="B70" s="32">
+      <c r="B70" s="33">
         <v>12.59</v>
       </c>
-      <c r="C70" s="32">
+      <c r="C70" s="33">
         <v>14.9</v>
       </c>
-      <c r="D70" s="32">
+      <c r="D70" s="33">
         <v>12.24</v>
       </c>
-      <c r="E70" s="32">
+      <c r="E70" s="33">
         <v>66.94</v>
       </c>
-      <c r="F70" s="32">
+      <c r="F70" s="33">
         <v>17.36</v>
       </c>
-      <c r="G70" s="30">
+      <c r="G70" s="31">
         <v>119.65</v>
       </c>
-      <c r="H70" s="31"/>
+      <c r="H70" s="32"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="29" t="s">
+      <c r="A71" s="30" t="s">
         <v>326</v>
       </c>
-      <c r="B71" s="32">
+      <c r="B71" s="33">
         <v>18.32</v>
       </c>
-      <c r="C71" s="32">
+      <c r="C71" s="33">
         <v>22.28</v>
       </c>
-      <c r="D71" s="31"/>
-      <c r="E71" s="31"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="31"/>
-      <c r="H71" s="31"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
     </row>
     <row r="72" ht="15.75" customHeight="1"/>
     <row r="73" ht="15.75" customHeight="1"/>
